--- a/reports/report_Bank.sol.xlsx
+++ b/reports/report_Bank.sol.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vulnerabilities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool Outputs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-21 03:28:57</t>
+          <t>2026-05-06 11:51:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -507,7 +508,7 @@
         <v>17.7</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -535,11 +536,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -718,6 +719,445 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mythril</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Reentrancy (proxy)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Slither proxy detected Reentrancy via 'reentrancy-eth' detector</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Echidna</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>echidna_balance_never_negative</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Echidna fuzz test 'echidna_balance_never_negative' failed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Issues Found</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Error Location</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Total Calls</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Calldata</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Shrinking Attempts</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Execution Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Slither</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>reentrancy-eth</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reentrancy in DepositFunds.withdraw() (contracts/Bank.sol#31-39):
+	External calls:
+	- (sent,None) = msg.sender.call{value: bal}() (contracts/Bank.sol#35)
+	State variables written after the call(s):
+	- balances[msg.sender] = 0 (contracts/Bank.sol#38)
+	DepositFunds.balances (contracts/Bank.sol#25) can be used in cross function reentrancies:
+	- DepositFunds.balances (contracts/Bank.sol#25)
+	- DepositFunds.deposit() (contracts/Bank.sol#27-29)
+	- DepositFunds.withdraw() (contracts/Bank.sol#31-39)
+</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[31, 32, 33, 34, 35, 36, 37, 38, 39]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Slither</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>solc-version</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Version constraint ^0.8.13 contains known severe issues (https://solidity.readthedocs.io/en/latest/bugs.html)
+	- VerbatimInvalidDeduplication
+	- FullInlinerNonExpressionSplitArgumentEvaluationOrder
+	- MissingSideEffectsOnSelectorAccess
+	- StorageWriteRemovalBeforeConditionalTermination
+	- AbiReencodingHeadOverflowWithStaticArrayCleanup
+	- DirtyBytesArrayToStorage
+	- InlineAssemblyMemorySideEffects
+	- DataLocationChangeInInternalOverride
+	- NestedCalldataArrayAbiReencodingSizeValidation.
+It is used by:
+	- ^0.8.13 (contracts/Bank.sol#22)
+</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>^0.8.13</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[22]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Slither</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>low-level-calls</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Informational</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low level call in DepositFunds.withdraw() (contracts/Bank.sol#31-39):
+	- (sent,None) = msg.sender.call{value: bal}() (contracts/Bank.sol#35)
+</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[31, 32, 33, 34, 35, 36, 37, 38, 39]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mythril</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Reentrancy (proxy)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Slither proxy detected Reentrancy via 'reentrancy-eth' detector</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Echidna</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>echidna_balance_never_negative</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Echidna fuzz test 'echidna_balance_never_negative' failed.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
